--- a/tugas/tugas10/notebook/latihan1_knn.xlsx
+++ b/tugas/tugas10/notebook/latihan1_knn.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\machine_learning\tugas\tugas10\notebook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{35B9363E-8120-40C4-83D4-6D3E9FA83A4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2954E7F-6BA7-4192-A89B-EF30A76C3470}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{F3F3A935-7792-4174-AE43-09AE4306B9A5}"/>
   </bookViews>
